--- a/fig2/boxplotSampleCounts.xlsx
+++ b/fig2/boxplotSampleCounts.xlsx
@@ -726,7 +726,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -734,7 +734,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +767,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -778,7 +778,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -789,7 +789,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -800,7 +800,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +833,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -844,7 +844,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -855,7 +855,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -866,7 +866,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +893,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -901,7 +901,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
